--- a/Testes/reescala/Teste seleção e cruzamento/Teste20/melhor_media_fitness.xlsx
+++ b/Testes/reescala/Teste seleção e cruzamento/Teste20/melhor_media_fitness.xlsx
@@ -4632,7 +4632,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
